--- a/docs/기능명세서.xlsx
+++ b/docs/기능명세서.xlsx
@@ -709,8 +709,8 @@
       <c r="F6" s="4" t="inlineStr">
         <is>
           <t>* 관리자만 접근 가능.
-* 사용자 상태: active, inactive, suspended.
-* 12개 권한 항목: note:read, note:write, note:sign, note:delete, template:read, template:write, inventory:read, inventory:write, scheduler:read, scheduler:write, audit:read, admin.
+* 사용자 상태: 활성(active), 비활성(inactive), 정지(suspended).
+* 12개 권한 항목: 노트 조회/작성/서명/삭제, 템플릿 조회/작성, 인벤토리 조회/작성, 예약 조회/작성, 감사로그 조회, 전체 관리 등.
 * 같은 사용자를 한 팀에 두 번 추가할 수 없습니다.
 * 모든 관리 작업은 감사로그에 자동 기록.</t>
         </is>

--- a/docs/기능명세서.xlsx
+++ b/docs/기능명세서.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\INTERWEB\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vscode\lab\lab-companion-feature-phase1-backend-infra\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19305C2A-D238-4437-8A4F-C0F56C3C864A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25949D9B-C7E3-4B51-91BD-067FEC504E2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="44880" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -345,13 +345,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>1. 프로토콜(템플릿) 관리 페이지에서 등록된 템플릿 목록을 확인합니다.
-2. "새 템플릿" 버튼으로 제목, 카테고리, 내용, 태그를 입력하여 생성합니다.
-3. "복사" 버튼으로 기존 템플릿을 복제합니다 
-4. "노트 작성" 버튼으로 해당 템플릿 기반 노트를 바로 생성할 수 있습니다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>1. 템플릿 목록에서 원하는 템플릿의 "노트 작성" 버튼을 클릭합니다.
 2. 노트 편집기에서 내용을 수정하고 저장합니다.
 3. 저장 시 원본 템플릿의 사용수가 자동 증가합니다.</t>
@@ -685,12 +678,19 @@
  </t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
+  <si>
+    <t>1. 템플릿 관리 페이지에서 등록된 템플릿 목록을 확인합니다.
+2. "새 템플릿" 버튼으로 제목, 카테고리, 내용, 태그를 입력하여 생성합니다.
+3. "복사" 버튼으로 기존 템플릿을 복제합니다 
+4. "노트 작성" 버튼으로 해당 템플릿 기반 노트를 바로 생성할 수 있습니다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -727,8 +727,15 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -739,6 +746,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF2F5496"/>
         <bgColor rgb="FF2F5496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -769,7 +782,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -781,6 +794,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1124,7 +1143,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="118.5" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:6" ht="139.5" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -1144,7 +1163,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="87.75" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:6" ht="113.65" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A4" s="2">
         <v>2</v>
       </c>
@@ -1175,10 +1194,10 @@
         <v>45</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>46</v>
@@ -1208,7 +1227,7 @@
       <c r="A7" s="2">
         <v>5</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -1295,10 +1314,10 @@
         <v>70</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>71</v>
+        <v>121</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>69</v>
@@ -1315,13 +1334,13 @@
         <v>18</v>
       </c>
       <c r="D12" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="F12" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="105.75" customHeight="1" x14ac:dyDescent="0.6">
@@ -1332,16 +1351,16 @@
         <v>19</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="114.75" customHeight="1" x14ac:dyDescent="0.6">
@@ -1358,10 +1377,10 @@
         <v>22</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="84.75" customHeight="1" x14ac:dyDescent="0.6">
@@ -1378,10 +1397,10 @@
         <v>25</v>
       </c>
       <c r="E15" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="130.5" customHeight="1" x14ac:dyDescent="0.6">
@@ -1392,13 +1411,13 @@
         <v>26</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>86</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>27</v>
@@ -1412,16 +1431,16 @@
         <v>28</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D17" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="99.75" customHeight="1" x14ac:dyDescent="0.6">
@@ -1435,13 +1454,13 @@
         <v>30</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E18" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="156.75" customHeight="1" x14ac:dyDescent="0.6">
@@ -1455,13 +1474,13 @@
         <v>32</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E19" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F19" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="112.5" customHeight="1" x14ac:dyDescent="0.6">
@@ -1475,13 +1494,13 @@
         <v>34</v>
       </c>
       <c r="D20" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="78.75" customHeight="1" x14ac:dyDescent="0.6">
@@ -1492,16 +1511,16 @@
         <v>35</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="E21" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>109</v>
-      </c>
       <c r="F21" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="99.75" customHeight="1" x14ac:dyDescent="0.6">
@@ -1509,16 +1528,16 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>36</v>
@@ -1532,16 +1551,16 @@
         <v>37</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="E23" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="2" t="s">
         <v>117</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.6">
@@ -1552,36 +1571,36 @@
         <v>38</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="120" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A25" s="2">
         <v>23</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="6" t="s">
         <v>39</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D25" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F25" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>121</v>
       </c>
     </row>
   </sheetData>
